--- a/AAII_Financials/Quarterly/RKUNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RKUNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>RKUNY</t>
   </si>
@@ -656,94 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -780,32 +783,35 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>3987400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3005200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3054800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2888500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3305700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8656100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5833500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2877600</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -842,32 +848,35 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>4469400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3510100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3608900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3583900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3857900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10129000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6794400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3366900</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -904,32 +913,35 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>-482000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-504900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-554100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-695400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-552200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-1472900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-960900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-489300</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -952,8 +964,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,8 +1027,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1076,8 +1092,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1114,32 +1133,35 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>40000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>13200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>28200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>21800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1176,8 +1198,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1200,8 +1222,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1221,8 +1246,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1259,32 +1285,35 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>4546100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3606200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3631300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3640100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3899000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9437400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6575000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3152100</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1321,32 +1350,35 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>-558600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-601000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-576600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-751500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-593300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-781300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-741500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-274400</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1369,8 +1401,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1407,32 +1440,35 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-74700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-39100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-14500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>16300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>104200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>73400</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1469,32 +1505,35 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>-135100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-169300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-186000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-366000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-216800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>247600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>48100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>133300</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1531,32 +1570,35 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>60400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>45400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>41600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>95300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>64800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1593,32 +1635,35 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>-693800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-649200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-653000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-791900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-641100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-860300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-702100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-232500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1655,32 +1700,35 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>124600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-103500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-67200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-177500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-430400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-102000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-129100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1741,8 +1789,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1779,32 +1830,35 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>-818400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-545700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-585800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-614400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-210600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-758200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-572900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-273600</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1841,32 +1895,35 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>-814200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-580000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-609800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-205600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-749200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-566600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-270400</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1927,8 +1984,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1965,8 +2025,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1989,8 +2049,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2051,8 +2114,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2113,8 +2179,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2151,32 +2220,35 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>74700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>39100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>14500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-16300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-104200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-73400</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2213,32 +2285,35 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>-814200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-580000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-609800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-205600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-749200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-566600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-270400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2299,8 +2374,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2337,99 +2415,105 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>-814200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-580000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-609800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-205600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-749200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-566600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-270400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2452,8 +2536,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2476,109 +2561,113 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27626100</v>
+      </c>
+      <c r="E41" s="3">
         <v>37232200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37284300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39250000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36939000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35497200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36376300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31499400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34619800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31499400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34619800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33883200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33330000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29164000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29632900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28771400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30298800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27698700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>27185000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>23742600</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2283300</v>
+      </c>
+      <c r="E42" s="3">
         <v>3132500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2615000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1838000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1274400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1437200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1292600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1116000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1156400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1116000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1156400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1166400</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2600,70 +2689,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24773900</v>
+      </c>
+      <c r="E43" s="3">
         <v>26189700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25570800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24925300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20839900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21788300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24100500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20883700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20755700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20883700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20755700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22254400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5171400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1907700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1884300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1796900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4229500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1626400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1562600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1613400</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2700,8 +2795,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2724,47 +2819,50 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>117990500</v>
+      </c>
+      <c r="E45" s="3">
         <v>97974600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>95916800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>82838100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>74051500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>77237200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>76061700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>68965700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>70600000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>68965700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>70600000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>71932600</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -2786,256 +2884,271 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>172673700</v>
+      </c>
+      <c r="E46" s="3">
         <v>164529100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>161386900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>148851500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>133104800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>135959800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>137831000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>122464800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>127131900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>122464800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>127131900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>129236600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35915700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31071800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31517300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30568300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32413500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>29325100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>28747600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>25356000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4850900</v>
+      </c>
+      <c r="E47" s="3">
         <v>5029700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4853800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4631200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5219200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4868100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4893700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4883100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4554600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4883100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4554600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4651900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>91121300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>75414300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>75018100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>71561200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>69465700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>66572800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>63111200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>60209000</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6600100</v>
+      </c>
+      <c r="E48" s="3">
         <v>6815000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8023400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7532000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7685400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8310600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8994200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8504400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8858900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8504400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8858900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9673600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17922000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7664500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7836300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7288800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13401500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6247400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6285200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5698300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6972600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6883200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7269200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6890800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6932500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7099700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7265800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6995100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7095300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6995100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7095300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7289800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13556700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6537300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6633700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5903800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11802600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5996900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5231400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4872200</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3096,8 +3209,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3158,8 +3274,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3196,32 +3315,35 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>10862700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5291000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5068100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4103200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5564300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3177100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3182700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3054000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3282,70 +3404,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>191552700</v>
+      </c>
+      <c r="E54" s="3">
         <v>183715600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>182134500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>168647300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>154341400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>157687800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>160508300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>144889600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>149725200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>144889600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>149725200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>153080000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>144856200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>125978900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>126073400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119425300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>115630500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>111319300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>106558100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>99189500</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3368,8 +3496,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3392,261 +3521,274 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2517700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3530800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2647200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3302100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2285200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2814500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2978700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2571400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2372400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2571400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2372400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2983800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3199000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2178300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2371000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2368300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2696200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2049200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1972800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2126600</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19627500</v>
+      </c>
+      <c r="E58" s="3">
         <v>35523300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36821800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34739300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>33800000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>33702900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>34017500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32225800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33715700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32225800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33715700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>37427400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7880500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5066400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3">
         <v>10962400</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>146983300</v>
+      </c>
+      <c r="E59" s="3">
         <v>130377700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>129420000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>117959900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>107068800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>109391600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>111188200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>98346700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101310000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>98346700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>101310000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>102271300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25377400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22163200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22122000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22121400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21359100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24053900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21386000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20542500</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>169128400</v>
+      </c>
+      <c r="E60" s="3">
         <v>169431700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>168889000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>156001200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>143153900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>145908900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>148184400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>133143900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>137398000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>133143900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>137398000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>142682400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>36456900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29407900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24492900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24489700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29880000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26103100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23358800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>22669100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>9879300</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -3679,93 +3821,99 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>30058900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26249600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>17099500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>26295000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19904700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20153200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19568300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18919300</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3807500</v>
+      </c>
+      <c r="E62" s="3">
         <v>4825600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4851000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4338200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3863800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4124300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4290800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3874600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3924000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3874600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3924000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4229700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>85286600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63866300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>77424600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>61640200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>65542100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>56834800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>55052800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>51111700</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3826,8 +3974,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3888,8 +4039,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3950,70 +4104,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>183442800</v>
+      </c>
+      <c r="E66" s="3">
         <v>175078200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>174245700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>160769700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>147329000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>150337100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>152791900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>137316100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>141617200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>137316100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>141617200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>147216800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>139237600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>119699700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>119199600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>112581700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>108116600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>103249400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>98145400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>92860000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4036,8 +4196,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4098,8 +4259,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4160,8 +4324,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4222,8 +4389,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4284,70 +4454,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5975200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6608500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6661700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5245500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4545100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4531000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4568500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3396300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3034300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3396300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3034300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2790200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1988600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-846400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-345200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>289300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>980100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1375200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1610500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1907200</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4408,8 +4584,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4470,8 +4649,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4532,70 +4714,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5631000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6329600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5583300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5901700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5346300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5636700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5934700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6533200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7041800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6533200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7041800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5428900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5618600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6279200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6873900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6843600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7513800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8069900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8412700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6329400</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4656,75 +4844,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4761,32 +4955,35 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>-814200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-540000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-580000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-609800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-205600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-749200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-566600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-270400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4809,70 +5006,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>489600</v>
+      </c>
+      <c r="E83" s="3">
         <v>515600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>543200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>513300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>515000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>542100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>549000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>478800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>480500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>478800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>480500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>487100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>514000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>441900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>440100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>392800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>391000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1012500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>685400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>334400</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4933,8 +5134,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4995,8 +5199,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5057,8 +5264,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5119,8 +5329,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5181,70 +5394,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1140600</v>
+      </c>
+      <c r="E89" s="3">
         <v>3223000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4184800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2362200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3212600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>984200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3990600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-523000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2506100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-523000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2506100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-922000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1345200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1380400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-148300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1388100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1133000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3012200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1782600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5267,70 +5486,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-202700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-93100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-116300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-129400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-255800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-326200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-218900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-328700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-218900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-328700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-508800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-104680000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-94123000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-132247000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-104168000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-117137000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-89955000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1116000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-523300</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5391,8 +5614,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5453,70 +5679,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>866200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-816500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1190500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-984400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1338000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1229500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1765600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-970800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-647900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-970800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-647900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-826400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-837200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1192300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1616800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2680000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1248800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3100700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2052700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5539,8 +5771,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5559,8 +5792,8 @@
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -5568,8 +5801,8 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
+      <c r="L96" s="3">
+        <v>0</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>8</v>
@@ -5577,8 +5810,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5587,22 +5820,25 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-47300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-44200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-45100</v>
       </c>
       <c r="V96" s="3">
         <v>-45100</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>-45100</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5663,8 +5899,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5725,8 +5964,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5787,190 +6029,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5430400</v>
+      </c>
+      <c r="E100" s="3">
         <v>751800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>213300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>355800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1622100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1777300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>835400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-560900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1512900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-560900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1512900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>295200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>488600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3652300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2129500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3515700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4005000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5907200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5161300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2260600</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E101" s="3">
         <v>64400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-60600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>41500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>96000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-121400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>43500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>78000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>43500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>78000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>56400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-113700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>40100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>71500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>45500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>17100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>96400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>87200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3394700</v>
+      </c>
+      <c r="E102" s="3">
         <v>3254200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3193600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1806500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3562500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1596400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2999800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2013200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3467000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2013200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3467000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1430300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>874700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1113900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>428200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-513000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3906300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5915100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4978400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1536000</v>
       </c>
     </row>
